--- a/artfynd/A 38359-2021 artfynd.xlsx
+++ b/artfynd/A 38359-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38359-2021 artfynd.xlsx
+++ b/artfynd/A 38359-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2259,6 +2259,2061 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120533201</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>458713</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6867696</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120531538</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>458339</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6867863</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120532730</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>458680</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6868004</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Konstnären vill inte ge sig till känna.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120532887</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>458610</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6867914</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120533045</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>458668</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6867737</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120533316</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>458733</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6867708</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>50 rosetter.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120532009</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>458615</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6867898</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120532232</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>458763</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6867919</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120532557</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>458741</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6867983</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120532867</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>658</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>458625</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6867932</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120532251</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>458778</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6867926</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120532432</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>458823</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6867946</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120532770</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>458672</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6867978</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120532450</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>458825</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6867932</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120533039</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>458668</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6867737</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120531612</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>658</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>458337</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6867876</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120531623</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>458345</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6867882</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120531883</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>458565</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6867871</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120532128</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78576</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>185</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>458714</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6867895</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120532030</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>458603</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6867860</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38359-2021 artfynd.xlsx
+++ b/artfynd/A 38359-2021 artfynd.xlsx
@@ -2261,10 +2261,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120533201</v>
+        <v>120532432</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2273,25 +2273,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458713</v>
+        <v>458823</v>
       </c>
       <c r="R15" t="n">
-        <v>6867696</v>
+        <v>6867946</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2363,10 +2363,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120531538</v>
+        <v>120532557</v>
       </c>
       <c r="B16" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2375,25 +2375,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458339</v>
+        <v>458741</v>
       </c>
       <c r="R16" t="n">
-        <v>6867863</v>
+        <v>6867983</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120532730</v>
+        <v>120532450</v>
       </c>
       <c r="B17" t="n">
         <v>79623</v>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458680</v>
+        <v>458825</v>
       </c>
       <c r="R17" t="n">
-        <v>6868004</v>
+        <v>6867932</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2541,11 +2541,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Konstnären vill inte ge sig till känna.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2572,10 +2567,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120532887</v>
+        <v>120532030</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>79652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2584,25 +2579,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2612,13 +2607,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458610</v>
+        <v>458603</v>
       </c>
       <c r="R18" t="n">
-        <v>6867914</v>
+        <v>6867860</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2776,7 +2771,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120533316</v>
+        <v>120531883</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2816,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458733</v>
+        <v>458565</v>
       </c>
       <c r="R20" t="n">
-        <v>6867708</v>
+        <v>6867871</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2852,11 +2847,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>50 rosetter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120532009</v>
+        <v>120533201</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2895,25 +2885,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2923,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458615</v>
+        <v>458713</v>
       </c>
       <c r="R21" t="n">
-        <v>6867898</v>
+        <v>6867696</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2985,7 +2975,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120532232</v>
+        <v>120532770</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3025,10 +3015,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458763</v>
+        <v>458672</v>
       </c>
       <c r="R22" t="n">
-        <v>6867919</v>
+        <v>6867978</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3087,7 +3077,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120532557</v>
+        <v>120532251</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3127,10 +3117,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458741</v>
+        <v>458778</v>
       </c>
       <c r="R23" t="n">
-        <v>6867983</v>
+        <v>6867926</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3189,10 +3179,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120532867</v>
+        <v>120532009</v>
       </c>
       <c r="B24" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3205,21 +3195,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3229,10 +3219,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458625</v>
+        <v>458615</v>
       </c>
       <c r="R24" t="n">
-        <v>6867932</v>
+        <v>6867898</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3291,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120532251</v>
+        <v>120532867</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3303,25 +3293,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3331,13 +3321,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458778</v>
+        <v>458625</v>
       </c>
       <c r="R25" t="n">
-        <v>6867926</v>
+        <v>6867932</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3393,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120532432</v>
+        <v>120532887</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3409,21 +3399,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3433,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458823</v>
+        <v>458610</v>
       </c>
       <c r="R26" t="n">
-        <v>6867946</v>
+        <v>6867914</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3495,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120532770</v>
+        <v>120533039</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3507,25 +3497,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3535,10 +3525,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458672</v>
+        <v>458668</v>
       </c>
       <c r="R27" t="n">
-        <v>6867978</v>
+        <v>6867737</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3597,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120532450</v>
+        <v>120532232</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3609,25 +3599,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3637,13 +3627,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458825</v>
+        <v>458763</v>
       </c>
       <c r="R28" t="n">
-        <v>6867932</v>
+        <v>6867919</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3699,10 +3689,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120533039</v>
+        <v>120531612</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3715,21 +3705,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3739,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458668</v>
+        <v>458337</v>
       </c>
       <c r="R29" t="n">
-        <v>6867737</v>
+        <v>6867876</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3775,6 +3765,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3801,10 +3796,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120531612</v>
+        <v>120533316</v>
       </c>
       <c r="B30" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3813,25 +3808,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3841,10 +3836,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458337</v>
+        <v>458733</v>
       </c>
       <c r="R30" t="n">
-        <v>6867876</v>
+        <v>6867708</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3881,7 +3876,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>10 fruktkroppar.</t>
+          <t>50 rosetter.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3908,10 +3903,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120531623</v>
+        <v>120531538</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>78278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3924,21 +3919,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3948,10 +3943,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458345</v>
+        <v>458339</v>
       </c>
       <c r="R31" t="n">
-        <v>6867882</v>
+        <v>6867863</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4010,10 +4005,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120531883</v>
+        <v>120531623</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4022,25 +4017,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4050,10 +4045,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458565</v>
+        <v>458345</v>
       </c>
       <c r="R32" t="n">
-        <v>6867871</v>
+        <v>6867882</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4214,10 +4209,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120532030</v>
+        <v>120532730</v>
       </c>
       <c r="B34" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4226,25 +4221,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4254,13 +4249,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458603</v>
+        <v>458680</v>
       </c>
       <c r="R34" t="n">
-        <v>6867860</v>
+        <v>6868004</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4290,6 +4285,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Konstnären vill inte ge sig till känna.</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 38359-2021 artfynd.xlsx
+++ b/artfynd/A 38359-2021 artfynd.xlsx
@@ -2771,7 +2771,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120531883</v>
+        <v>120533201</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458565</v>
+        <v>458713</v>
       </c>
       <c r="R20" t="n">
-        <v>6867871</v>
+        <v>6867696</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2873,7 +2873,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120533201</v>
+        <v>120531883</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458713</v>
+        <v>458565</v>
       </c>
       <c r="R21" t="n">
-        <v>6867696</v>
+        <v>6867871</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>

--- a/artfynd/A 38359-2021 artfynd.xlsx
+++ b/artfynd/A 38359-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102963755</v>
+        <v>120532128</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458656.2280386837</v>
+        <v>458714</v>
       </c>
       <c r="R2" t="n">
-        <v>6868007.379835112</v>
+        <v>6867895</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,63 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102963661</v>
+        <v>120531612</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härjåbron SÖ, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458602.1255864465</v>
+        <v>458337</v>
       </c>
       <c r="R3" t="n">
-        <v>6867783.954878522</v>
+        <v>6867876</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,63 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102963796</v>
+        <v>120532867</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458566.1245314921</v>
+        <v>458625</v>
       </c>
       <c r="R4" t="n">
-        <v>6867925.151598694</v>
+        <v>6867932</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,63 +971,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102963730</v>
+        <v>120531623</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458712.1451155503</v>
+        <v>458345</v>
       </c>
       <c r="R5" t="n">
-        <v>6867992.108587649</v>
+        <v>6867882</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,22 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,63 +1068,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102963784</v>
+        <v>120532887</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458588.0258258758</v>
+        <v>458610</v>
       </c>
       <c r="R6" t="n">
-        <v>6867942.774011833</v>
+        <v>6867914</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,22 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,63 +1165,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102963680</v>
+        <v>120533500</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Härjåbron SÖ, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458649.5691941103</v>
+        <v>458382</v>
       </c>
       <c r="R7" t="n">
-        <v>6867808.329769267</v>
+        <v>6867765</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,22 +1230,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102963765</v>
+        <v>120532009</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,47 +1273,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458638.624165976</v>
+        <v>458615</v>
       </c>
       <c r="R8" t="n">
-        <v>6867955.340431518</v>
+        <v>6867898</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,22 +1327,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,63 +1359,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102963699</v>
+        <v>120531538</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Härjåbron SÖ, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458693.3310352432</v>
+        <v>458339</v>
       </c>
       <c r="R9" t="n">
-        <v>6867917.95784812</v>
+        <v>6867863</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1609,22 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,63 +1456,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102963685</v>
+        <v>120532432</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Härjåbron SÖ, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458689.3566656439</v>
+        <v>458823</v>
       </c>
       <c r="R10" t="n">
-        <v>6867745.704617788</v>
+        <v>6867946</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1731,22 +1521,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,63 +1553,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102963779</v>
+        <v>120532450</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458608.9784067955</v>
+        <v>458825</v>
       </c>
       <c r="R11" t="n">
-        <v>6867959.937243088</v>
+        <v>6867932</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1853,22 +1618,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,63 +1650,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102963693</v>
+        <v>120532730</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Härjåbron SÖ, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458731.3295760637</v>
+        <v>458680</v>
       </c>
       <c r="R12" t="n">
-        <v>6867746.608309188</v>
+        <v>6868004</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1975,22 +1715,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Konstnären vill inte ge sig till känna.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,63 +1752,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102963708</v>
+        <v>120533039</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458719.6187483667</v>
+        <v>458668</v>
       </c>
       <c r="R13" t="n">
-        <v>6867986.369056409</v>
+        <v>6867737</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2097,22 +1817,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,63 +1849,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102963667</v>
+        <v>120532030</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Härjåbron SÖ, Hjd</t>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458616.102031524</v>
+        <v>458603</v>
       </c>
       <c r="R14" t="n">
-        <v>6867770.132561125</v>
+        <v>6867860</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,22 +1914,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,12 +1949,7 @@
         <v>120533045</v>
       </c>
       <c r="B15" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2363,15 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120533316</v>
+        <v>102963661</v>
       </c>
       <c r="B16" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,20 +2071,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458733</v>
+        <v>458602</v>
       </c>
       <c r="R16" t="n">
-        <v>6867708</v>
+        <v>6867784</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2433,17 +2118,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>50 rosetter.</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,53 +2150,58 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120531538</v>
+        <v>102963667</v>
       </c>
       <c r="B17" t="n">
-        <v>78330</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458339</v>
+        <v>458616</v>
       </c>
       <c r="R17" t="n">
-        <v>6867863</v>
+        <v>6867770</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2540,12 +2225,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2572,53 +2257,58 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120531612</v>
+        <v>102963680</v>
       </c>
       <c r="B18" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458337</v>
+        <v>458650</v>
       </c>
       <c r="R18" t="n">
-        <v>6867876</v>
+        <v>6867809</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2642,17 +2332,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar.</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2679,53 +2364,58 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120533039</v>
+        <v>102963685</v>
       </c>
       <c r="B19" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458668</v>
+        <v>458690</v>
       </c>
       <c r="R19" t="n">
-        <v>6867737</v>
+        <v>6867746</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2749,12 +2439,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2781,15 +2471,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120532251</v>
+        <v>102963693</v>
       </c>
       <c r="B20" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,20 +2499,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458778</v>
+        <v>458732</v>
       </c>
       <c r="R20" t="n">
-        <v>6867926</v>
+        <v>6867746</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2851,12 +2546,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,53 +2578,58 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120531623</v>
+        <v>102963699</v>
       </c>
       <c r="B21" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron SÖ, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458345</v>
+        <v>458693</v>
       </c>
       <c r="R21" t="n">
-        <v>6867882</v>
+        <v>6867918</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2953,12 +2653,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,15 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120531883</v>
+        <v>102963708</v>
       </c>
       <c r="B22" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3018,20 +2713,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458565</v>
+        <v>458719</v>
       </c>
       <c r="R22" t="n">
-        <v>6867871</v>
+        <v>6867986</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3055,12 +2760,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,53 +2792,58 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120532867</v>
+        <v>102963730</v>
       </c>
       <c r="B23" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458625</v>
+        <v>458712</v>
       </c>
       <c r="R23" t="n">
-        <v>6867932</v>
+        <v>6867992</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3157,12 +2867,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,53 +2899,58 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120532730</v>
+        <v>102963755</v>
       </c>
       <c r="B24" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458680</v>
+        <v>458656</v>
       </c>
       <c r="R24" t="n">
-        <v>6868004</v>
+        <v>6868008</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3259,17 +2974,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Konstnären vill inte ge sig till känna.</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3296,53 +3006,58 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120532128</v>
+        <v>102963765</v>
       </c>
       <c r="B25" t="n">
-        <v>78628</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458714</v>
+        <v>458639</v>
       </c>
       <c r="R25" t="n">
-        <v>6867895</v>
+        <v>6867955</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3366,12 +3081,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,53 +3113,58 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120532887</v>
+        <v>102963779</v>
       </c>
       <c r="B26" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458610</v>
+        <v>458609</v>
       </c>
       <c r="R26" t="n">
-        <v>6867914</v>
+        <v>6867960</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3468,12 +3188,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,15 +3220,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120532770</v>
+        <v>102963784</v>
       </c>
       <c r="B27" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,20 +3248,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458672</v>
+        <v>458588</v>
       </c>
       <c r="R27" t="n">
-        <v>6867978</v>
+        <v>6867943</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3570,12 +3295,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,15 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120533201</v>
+        <v>102963796</v>
       </c>
       <c r="B28" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,20 +3355,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+          <t>Härjåbron Ö, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458713</v>
+        <v>458566</v>
       </c>
       <c r="R28" t="n">
-        <v>6867696</v>
+        <v>6867925</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3672,12 +3402,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,37 +3434,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120532030</v>
+        <v>120531883</v>
       </c>
       <c r="B29" t="n">
-        <v>79704</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3744,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458603</v>
+        <v>458565</v>
       </c>
       <c r="R29" t="n">
-        <v>6867860</v>
+        <v>6867871</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3806,37 +3531,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120532450</v>
+        <v>120532232</v>
       </c>
       <c r="B30" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3846,13 +3566,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458825</v>
+        <v>458763</v>
       </c>
       <c r="R30" t="n">
-        <v>6867932</v>
+        <v>6867919</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3908,37 +3628,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120532009</v>
+        <v>120532251</v>
       </c>
       <c r="B31" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3948,13 +3663,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458615</v>
+        <v>458778</v>
       </c>
       <c r="R31" t="n">
-        <v>6867898</v>
+        <v>6867926</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,37 +3725,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120532432</v>
+        <v>120532557</v>
       </c>
       <c r="B32" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4050,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458823</v>
+        <v>458741</v>
       </c>
       <c r="R32" t="n">
-        <v>6867946</v>
+        <v>6867983</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4112,15 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120532232</v>
+        <v>120532770</v>
       </c>
       <c r="B33" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,10 +3857,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458763</v>
+        <v>458672</v>
       </c>
       <c r="R33" t="n">
-        <v>6867919</v>
+        <v>6867978</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4214,15 +3919,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120532557</v>
+        <v>120533116</v>
       </c>
       <c r="B34" t="n">
-        <v>98054</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,13 +3954,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458741</v>
+        <v>458667</v>
       </c>
       <c r="R34" t="n">
-        <v>6867983</v>
+        <v>6867694</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4313,6 +4013,205 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120533201</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>458713</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6867696</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120533316</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Härjåbron Ö, Härjåbron Ö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>458733</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6867708</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>50 rosetter.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
